--- a/interpretacao/resultados_modelos_10fold.xlsx
+++ b/interpretacao/resultados_modelos_10fold.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vitoria-vaz\estudos\UFU\projeto-graduacao\pg-amamentacao\interpretacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CD71A2-D7C4-45FC-AE89-DEF12BFADF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B01CEBE-35F8-439E-AEAA-0C663CEC0DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-6555" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Métricas" sheetId="1" r:id="rId1"/>
     <sheet name="Matrizes de Confusão" sheetId="2" r:id="rId2"/>
+    <sheet name="Consolidado por Algoritmo" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="33">
   <si>
     <t>Quantidade Atributos</t>
   </si>
@@ -47,7 +48,7 @@
     <t>AUC-ROC</t>
   </si>
   <si>
-    <t>treino_e_teste_1</t>
+    <t>selecionado_por_especialistas</t>
   </si>
   <si>
     <t>Decision Tree</t>
@@ -60,6 +61,9 @@
   </si>
   <si>
     <t>XGBoost</t>
+  </si>
+  <si>
+    <t>treino_e_teste_1</t>
   </si>
   <si>
     <t>treino_e_teste_2</t>
@@ -77,23 +81,53 @@
     <t>treino_e_teste_todos</t>
   </si>
   <si>
-    <t>Verdadeiros Negativos (VN)</t>
+    <t>Verdadeiros Negativos (VN) [Real: Desmame, Previsto: Desmame]</t>
   </si>
   <si>
-    <t>Falsos Positivos (FP)</t>
+    <t>Falsos Positivos (FP) [Real: Desmame, Previsto: Sucesso]</t>
   </si>
   <si>
-    <t>Falsos Negativos (FN)</t>
+    <t>Falsos Negativos (FN) [Real: Sucesso, Previsto: Desmame]</t>
   </si>
   <si>
-    <t>Verdadeiros Positivos (VP)</t>
+    <t>Verdadeiros Positivos (VP) [Real: Sucesso, Previsto: Sucesso]</t>
+  </si>
+  <si>
+    <t>Acurácia_mean</t>
+  </si>
+  <si>
+    <t>Acurácia_std</t>
+  </si>
+  <si>
+    <t>Sensibilidade_mean</t>
+  </si>
+  <si>
+    <t>Sensibilidade_std</t>
+  </si>
+  <si>
+    <t>Especificidade_mean</t>
+  </si>
+  <si>
+    <t>Especificidade_std</t>
+  </si>
+  <si>
+    <t>F1-Score_mean</t>
+  </si>
+  <si>
+    <t>F1-Score_std</t>
+  </si>
+  <si>
+    <t>AUC-ROC_mean</t>
+  </si>
+  <si>
+    <t>AUC-ROC_std</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,13 +140,50 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -142,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -150,6 +221,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,13 +541,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:V49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="18.140625" customWidth="1"/>
+    <col min="1" max="8" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -484,1149 +573,1589 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:22" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>10</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="7">
+        <v>0.52790000000000004</v>
+      </c>
+      <c r="E2" s="7">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="F2" s="7">
+        <v>0.65939999999999999</v>
+      </c>
+      <c r="G2" s="7">
+        <v>0.37930000000000003</v>
+      </c>
+      <c r="H2" s="7">
+        <v>0.51719999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
+        <v>10</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0.54349999999999998</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.37819999999999998</v>
+      </c>
+      <c r="F3" s="9">
+        <v>0.6623</v>
+      </c>
+      <c r="G3" s="9">
+        <v>0.4093</v>
+      </c>
+      <c r="H3" s="9">
+        <v>0.53610000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>10</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0.52410000000000001</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0.69789999999999996</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0.39910000000000001</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0.55089999999999995</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0.57020000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>10</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0.5554</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.31359999999999999</v>
+      </c>
+      <c r="F5" s="9">
+        <v>0.72909999999999997</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0.37109999999999999</v>
+      </c>
+      <c r="H5" s="9">
+        <v>0.5413</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="4">
         <v>0.58340000000000003</v>
       </c>
-      <c r="E2">
+      <c r="E6" s="4">
         <v>0.39689999999999998</v>
       </c>
-      <c r="F2">
+      <c r="F6" s="4">
         <v>0.71740000000000004</v>
       </c>
-      <c r="G2">
+      <c r="G6" s="4">
         <v>0.44350000000000001</v>
       </c>
-      <c r="H2">
+      <c r="H6" s="4">
         <v>0.59130000000000005</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3">
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
+    </row>
+    <row r="7" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>10</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7">
         <v>0.58160000000000001</v>
       </c>
-      <c r="E3">
+      <c r="E7">
         <v>0.41310000000000002</v>
       </c>
-      <c r="F3">
+      <c r="F7">
         <v>0.7026</v>
       </c>
-      <c r="G3">
+      <c r="G7">
         <v>0.45229999999999998</v>
       </c>
-      <c r="H3">
+      <c r="H7">
         <v>0.59860000000000002</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+    </row>
+    <row r="8" spans="1:22" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D4">
+      <c r="D8" s="4">
         <v>0.57769999999999999</v>
       </c>
-      <c r="E4">
+      <c r="E8" s="4">
         <v>0.63300000000000001</v>
       </c>
-      <c r="F4">
+      <c r="F8" s="4">
         <v>0.53779999999999994</v>
       </c>
-      <c r="G4">
+      <c r="G8" s="4">
         <v>0.55630000000000002</v>
       </c>
-      <c r="H4">
+      <c r="H8" s="4">
         <v>0.6119</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>0.59340000000000004</v>
-      </c>
-      <c r="E5">
-        <v>0.40899999999999997</v>
-      </c>
-      <c r="F5">
-        <v>0.72589999999999999</v>
-      </c>
-      <c r="G5">
-        <v>0.45689999999999997</v>
-      </c>
-      <c r="H5">
-        <v>0.61029999999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6">
-        <v>0.58740000000000003</v>
-      </c>
-      <c r="E6">
-        <v>0.36230000000000001</v>
-      </c>
-      <c r="F6">
-        <v>0.74929999999999997</v>
-      </c>
-      <c r="G6">
-        <v>0.42349999999999999</v>
-      </c>
-      <c r="H6">
-        <v>0.58950000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7">
-        <v>0.58350000000000002</v>
-      </c>
-      <c r="E7">
-        <v>0.38150000000000001</v>
-      </c>
-      <c r="F7">
-        <v>0.72870000000000001</v>
-      </c>
-      <c r="G7">
-        <v>0.43380000000000002</v>
-      </c>
-      <c r="H7">
-        <v>0.59750000000000003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8">
-        <v>0.57440000000000002</v>
-      </c>
-      <c r="E8">
-        <v>0.6482</v>
-      </c>
-      <c r="F8">
-        <v>0.52139999999999997</v>
-      </c>
-      <c r="G8">
-        <v>0.56020000000000003</v>
-      </c>
-      <c r="H8">
-        <v>0.6129</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+    </row>
+    <row r="9" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>10</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
       </c>
       <c r="D9">
+        <v>0.59340000000000004</v>
+      </c>
+      <c r="E9">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="F9">
+        <v>0.72589999999999999</v>
+      </c>
+      <c r="G9">
+        <v>0.45689999999999997</v>
+      </c>
+      <c r="H9">
+        <v>0.61029999999999995</v>
+      </c>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+    </row>
+    <row r="10" spans="1:22" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>10</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0.58740000000000003</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.36230000000000001</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0.74929999999999997</v>
+      </c>
+      <c r="G10" s="7">
+        <v>0.42349999999999999</v>
+      </c>
+      <c r="H10" s="7">
+        <v>0.58950000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0.58350000000000002</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.38150000000000001</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0.72870000000000001</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0.43380000000000002</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0.59750000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0.57440000000000002</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.6482</v>
+      </c>
+      <c r="F12" s="7">
+        <v>0.52139999999999997</v>
+      </c>
+      <c r="G12" s="7">
+        <v>0.56020000000000003</v>
+      </c>
+      <c r="H12" s="7">
+        <v>0.6129</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="9">
+        <v>10</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="9">
         <v>0.59230000000000005</v>
       </c>
-      <c r="E9">
+      <c r="E13" s="9">
         <v>0.37109999999999999</v>
       </c>
-      <c r="F9">
+      <c r="F13" s="9">
         <v>0.75119999999999998</v>
       </c>
-      <c r="G9">
+      <c r="G13" s="9">
         <v>0.43219999999999997</v>
       </c>
-      <c r="H9">
+      <c r="H13" s="9">
         <v>0.61550000000000005</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
+    <row r="14" spans="1:22" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D10">
+      <c r="D14" s="4">
         <v>0.56399999999999995</v>
       </c>
-      <c r="E10">
+      <c r="E14" s="4">
         <v>0.41149999999999998</v>
       </c>
-      <c r="F10">
+      <c r="F14" s="4">
         <v>0.67359999999999998</v>
       </c>
-      <c r="G10">
+      <c r="G14" s="4">
         <v>0.44109999999999999</v>
       </c>
-      <c r="H10">
+      <c r="H14" s="4">
         <v>0.56089999999999995</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11">
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
+      <c r="V14" s="6"/>
+    </row>
+    <row r="15" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>10</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15">
         <v>0.58030000000000004</v>
       </c>
-      <c r="E11">
+      <c r="E15">
         <v>0.434</v>
       </c>
-      <c r="F11">
+      <c r="F15">
         <v>0.68540000000000001</v>
       </c>
-      <c r="G11">
+      <c r="G15">
         <v>0.46379999999999999</v>
       </c>
-      <c r="H11">
+      <c r="H15">
         <v>0.58640000000000003</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+    </row>
+    <row r="16" spans="1:22" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>10</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D12">
+      <c r="D16" s="4">
         <v>0.5897</v>
       </c>
-      <c r="E12">
+      <c r="E16" s="4">
         <v>0.54869999999999997</v>
       </c>
-      <c r="F12">
+      <c r="F16" s="4">
         <v>0.61919999999999997</v>
       </c>
-      <c r="G12">
+      <c r="G16" s="4">
         <v>0.52800000000000002</v>
       </c>
-      <c r="H12">
+      <c r="H16" s="4">
         <v>0.61429999999999996</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>10</v>
-      </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13">
-        <v>0.58779999999999999</v>
-      </c>
-      <c r="E13">
-        <v>0.4118</v>
-      </c>
-      <c r="F13">
-        <v>0.71430000000000005</v>
-      </c>
-      <c r="G13">
-        <v>0.45519999999999999</v>
-      </c>
-      <c r="H13">
-        <v>0.60289999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>10</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14">
-        <v>0.57809999999999995</v>
-      </c>
-      <c r="E14">
-        <v>0.36830000000000002</v>
-      </c>
-      <c r="F14">
-        <v>0.72889999999999999</v>
-      </c>
-      <c r="G14">
-        <v>0.42199999999999999</v>
-      </c>
-      <c r="H14">
-        <v>0.54849999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>10</v>
-      </c>
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15">
-        <v>0.58009999999999995</v>
-      </c>
-      <c r="E15">
-        <v>0.40789999999999998</v>
-      </c>
-      <c r="F15">
-        <v>0.70379999999999998</v>
-      </c>
-      <c r="G15">
-        <v>0.44829999999999998</v>
-      </c>
-      <c r="H15">
-        <v>0.57179999999999997</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>10</v>
-      </c>
-      <c r="B16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16">
-        <v>0.59099999999999997</v>
-      </c>
-      <c r="E16">
-        <v>0.1946</v>
-      </c>
-      <c r="F16">
-        <v>0.87590000000000001</v>
-      </c>
-      <c r="G16">
-        <v>0.28470000000000001</v>
-      </c>
-      <c r="H16">
-        <v>0.59870000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="6"/>
+      <c r="T16" s="6"/>
+      <c r="U16" s="6"/>
+      <c r="V16" s="6"/>
+    </row>
+    <row r="17" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>10</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
       </c>
       <c r="D17">
+        <v>0.58779999999999999</v>
+      </c>
+      <c r="E17">
+        <v>0.4118</v>
+      </c>
+      <c r="F17">
+        <v>0.71430000000000005</v>
+      </c>
+      <c r="G17">
+        <v>0.45519999999999999</v>
+      </c>
+      <c r="H17">
+        <v>0.60289999999999999</v>
+      </c>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
+      <c r="U17" s="6"/>
+      <c r="V17" s="6"/>
+    </row>
+    <row r="18" spans="1:22" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>10</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0.57809999999999995</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.36830000000000002</v>
+      </c>
+      <c r="F18" s="7">
+        <v>0.72889999999999999</v>
+      </c>
+      <c r="G18" s="7">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0.54849999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="9">
+        <v>10</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0.58009999999999995</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0.40789999999999998</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0.70379999999999998</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0.44829999999999998</v>
+      </c>
+      <c r="H19" s="9">
+        <v>0.57179999999999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>10</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="7">
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.1946</v>
+      </c>
+      <c r="F20" s="7">
+        <v>0.87590000000000001</v>
+      </c>
+      <c r="G20" s="7">
+        <v>0.28470000000000001</v>
+      </c>
+      <c r="H20" s="7">
+        <v>0.59870000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
+        <v>10</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="9">
         <v>0.59060000000000001</v>
       </c>
-      <c r="E17">
+      <c r="E21" s="9">
         <v>0.3664</v>
       </c>
-      <c r="F17">
+      <c r="F21" s="9">
         <v>0.75180000000000002</v>
       </c>
-      <c r="G17">
+      <c r="G21" s="9">
         <v>0.42809999999999998</v>
       </c>
-      <c r="H17">
+      <c r="H21" s="9">
         <v>0.59399999999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>10</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="s">
+    <row r="22" spans="1:22" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>10</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D18">
+      <c r="D22" s="4">
         <v>0.55720000000000003</v>
       </c>
-      <c r="E18">
+      <c r="E22" s="4">
         <v>0.39360000000000001</v>
       </c>
-      <c r="F18">
+      <c r="F22" s="4">
         <v>0.67479999999999996</v>
       </c>
-      <c r="G18">
+      <c r="G22" s="4">
         <v>0.4264</v>
       </c>
-      <c r="H18">
+      <c r="H22" s="4">
         <v>0.55789999999999995</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>10</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19">
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+    </row>
+    <row r="23" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>10</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23">
         <v>0.56579999999999997</v>
       </c>
-      <c r="E19">
+      <c r="E23">
         <v>0.41920000000000002</v>
       </c>
-      <c r="F19">
+      <c r="F23">
         <v>0.67120000000000002</v>
       </c>
-      <c r="G19">
+      <c r="G23">
         <v>0.44679999999999997</v>
       </c>
-      <c r="H19">
+      <c r="H23">
         <v>0.57830000000000004</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>10</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
+      <c r="U23" s="6"/>
+      <c r="V23" s="6"/>
+    </row>
+    <row r="24" spans="1:22" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>10</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D20">
+      <c r="D24" s="4">
         <v>0.59330000000000005</v>
       </c>
-      <c r="E20">
+      <c r="E24" s="4">
         <v>0.44800000000000001</v>
       </c>
-      <c r="F20">
+      <c r="F24" s="4">
         <v>0.69769999999999999</v>
       </c>
-      <c r="G20">
+      <c r="G24" s="4">
         <v>0.47960000000000003</v>
       </c>
-      <c r="H20">
+      <c r="H24" s="4">
         <v>0.6179</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>10</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21">
-        <v>0.58819999999999995</v>
-      </c>
-      <c r="E21">
-        <v>0.42030000000000001</v>
-      </c>
-      <c r="F21">
-        <v>0.70899999999999996</v>
-      </c>
-      <c r="G21">
-        <v>0.46050000000000002</v>
-      </c>
-      <c r="H21">
-        <v>0.60750000000000004</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22">
-        <v>0.54959999999999998</v>
-      </c>
-      <c r="E22">
-        <v>0.44469999999999998</v>
-      </c>
-      <c r="F22">
-        <v>0.625</v>
-      </c>
-      <c r="G22">
-        <v>0.45229999999999998</v>
-      </c>
-      <c r="H22">
-        <v>0.54969999999999997</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23">
-        <v>0.58230000000000004</v>
-      </c>
-      <c r="E23">
-        <v>0.42580000000000001</v>
-      </c>
-      <c r="F23">
-        <v>0.69469999999999998</v>
-      </c>
-      <c r="G23">
-        <v>0.4602</v>
-      </c>
-      <c r="H23">
-        <v>0.58640000000000003</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24">
-        <v>0.5897</v>
-      </c>
-      <c r="E24">
-        <v>0.58520000000000005</v>
-      </c>
-      <c r="F24">
-        <v>0.59299999999999997</v>
-      </c>
-      <c r="G24">
-        <v>0.54400000000000004</v>
-      </c>
-      <c r="H24">
-        <v>0.61699999999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="6"/>
+      <c r="T24" s="6"/>
+      <c r="U24" s="6"/>
+      <c r="V24" s="6"/>
+    </row>
+    <row r="25" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
       </c>
       <c r="D25">
+        <v>0.58819999999999995</v>
+      </c>
+      <c r="E25">
+        <v>0.42030000000000001</v>
+      </c>
+      <c r="F25">
+        <v>0.70899999999999996</v>
+      </c>
+      <c r="G25">
+        <v>0.46050000000000002</v>
+      </c>
+      <c r="H25">
+        <v>0.60750000000000004</v>
+      </c>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="6"/>
+      <c r="T25" s="6"/>
+      <c r="U25" s="6"/>
+      <c r="V25" s="6"/>
+    </row>
+    <row r="26" spans="1:22" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>15</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="7">
+        <v>0.54959999999999998</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.44469999999999998</v>
+      </c>
+      <c r="F26" s="7">
+        <v>0.625</v>
+      </c>
+      <c r="G26" s="7">
+        <v>0.45229999999999998</v>
+      </c>
+      <c r="H26" s="7">
+        <v>0.54969999999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="9">
+        <v>15</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="9">
+        <v>0.58230000000000004</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0.42580000000000001</v>
+      </c>
+      <c r="F27" s="9">
+        <v>0.69469999999999998</v>
+      </c>
+      <c r="G27" s="9">
+        <v>0.4602</v>
+      </c>
+      <c r="H27" s="9">
+        <v>0.58640000000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>15</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="7">
+        <v>0.5897</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.58520000000000005</v>
+      </c>
+      <c r="F28" s="7">
+        <v>0.59299999999999997</v>
+      </c>
+      <c r="G28" s="7">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="H28" s="7">
+        <v>0.61699999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
+        <v>15</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="9">
         <v>0.59109999999999996</v>
       </c>
-      <c r="E25">
+      <c r="E29" s="9">
         <v>0.42880000000000001</v>
       </c>
-      <c r="F25">
+      <c r="F29" s="9">
         <v>0.70779999999999998</v>
       </c>
-      <c r="G25">
+      <c r="G29" s="9">
         <v>0.46729999999999999</v>
       </c>
-      <c r="H25">
+      <c r="H29" s="9">
         <v>0.60809999999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" t="s">
+    <row r="30" spans="1:22" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>15</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D26">
+      <c r="D30" s="4">
         <v>0.55489999999999995</v>
       </c>
-      <c r="E26">
+      <c r="E30" s="4">
         <v>0.44119999999999998</v>
       </c>
-      <c r="F26">
+      <c r="F30" s="4">
         <v>0.63660000000000005</v>
       </c>
-      <c r="G26">
+      <c r="G30" s="4">
         <v>0.45329999999999998</v>
       </c>
-      <c r="H26">
+      <c r="H30" s="4">
         <v>0.54849999999999999</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27">
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="6"/>
+      <c r="T30" s="6"/>
+      <c r="U30" s="6"/>
+      <c r="V30" s="6"/>
+    </row>
+    <row r="31" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>15</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31">
         <v>0.58420000000000005</v>
       </c>
-      <c r="E27">
+      <c r="E31">
         <v>0.44280000000000003</v>
       </c>
-      <c r="F27">
+      <c r="F31">
         <v>0.68579999999999997</v>
       </c>
-      <c r="G27">
+      <c r="G31">
         <v>0.47110000000000002</v>
       </c>
-      <c r="H27">
+      <c r="H31">
         <v>0.58819999999999995</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="6"/>
+      <c r="T31" s="6"/>
+      <c r="U31" s="6"/>
+      <c r="V31" s="6"/>
+    </row>
+    <row r="32" spans="1:22" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>15</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D28">
+      <c r="D32" s="4">
         <v>0.57709999999999995</v>
       </c>
-      <c r="E28">
+      <c r="E32" s="4">
         <v>0.66049999999999998</v>
       </c>
-      <c r="F28">
+      <c r="F32" s="4">
         <v>0.5171</v>
       </c>
-      <c r="G28">
+      <c r="G32" s="4">
         <v>0.56640000000000001</v>
       </c>
-      <c r="H28">
+      <c r="H32" s="4">
         <v>0.6159</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29">
-        <v>0.59350000000000003</v>
-      </c>
-      <c r="E29">
-        <v>0.43430000000000002</v>
-      </c>
-      <c r="F29">
-        <v>0.70799999999999996</v>
-      </c>
-      <c r="G29">
-        <v>0.47189999999999999</v>
-      </c>
-      <c r="H29">
-        <v>0.61199999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30">
-        <v>0.55900000000000005</v>
-      </c>
-      <c r="E30">
-        <v>0.46010000000000001</v>
-      </c>
-      <c r="F30">
-        <v>0.63009999999999999</v>
-      </c>
-      <c r="G30">
-        <v>0.46600000000000003</v>
-      </c>
-      <c r="H30">
-        <v>0.55220000000000002</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31">
-        <v>0.59209999999999996</v>
-      </c>
-      <c r="E31">
-        <v>0.4098</v>
-      </c>
-      <c r="F31">
-        <v>0.72319999999999995</v>
-      </c>
-      <c r="G31">
-        <v>0.45669999999999999</v>
-      </c>
-      <c r="H31">
-        <v>0.59719999999999995</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32">
-        <v>0.59030000000000005</v>
-      </c>
-      <c r="E32">
-        <v>0.54069999999999996</v>
-      </c>
-      <c r="F32">
-        <v>0.626</v>
-      </c>
-      <c r="G32">
-        <v>0.52470000000000006</v>
-      </c>
-      <c r="H32">
-        <v>0.61580000000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="6"/>
+      <c r="T32" s="6"/>
+      <c r="U32" s="6"/>
+      <c r="V32" s="6"/>
+    </row>
+    <row r="33" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>15</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
       </c>
       <c r="D33">
+        <v>0.59350000000000003</v>
+      </c>
+      <c r="E33">
+        <v>0.43430000000000002</v>
+      </c>
+      <c r="F33">
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="G33">
+        <v>0.47189999999999999</v>
+      </c>
+      <c r="H33">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6"/>
+      <c r="R33" s="6"/>
+      <c r="S33" s="6"/>
+      <c r="T33" s="6"/>
+      <c r="U33" s="6"/>
+      <c r="V33" s="6"/>
+    </row>
+    <row r="34" spans="1:22" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>15</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="7">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.46010000000000001</v>
+      </c>
+      <c r="F34" s="7">
+        <v>0.63009999999999999</v>
+      </c>
+      <c r="G34" s="7">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="H34" s="7">
+        <v>0.55220000000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="9">
+        <v>15</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="9">
+        <v>0.59209999999999996</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.4098</v>
+      </c>
+      <c r="F35" s="9">
+        <v>0.72319999999999995</v>
+      </c>
+      <c r="G35" s="9">
+        <v>0.45669999999999999</v>
+      </c>
+      <c r="H35" s="9">
+        <v>0.59719999999999995</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>15</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="7">
+        <v>0.59030000000000005</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.54069999999999996</v>
+      </c>
+      <c r="F36" s="7">
+        <v>0.626</v>
+      </c>
+      <c r="G36" s="7">
+        <v>0.52470000000000006</v>
+      </c>
+      <c r="H36" s="7">
+        <v>0.61580000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="9">
+        <v>15</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" s="9">
         <v>0.59040000000000004</v>
       </c>
-      <c r="E33">
+      <c r="E37" s="9">
         <v>0.42</v>
       </c>
-      <c r="F33">
+      <c r="F37" s="9">
         <v>0.71289999999999998</v>
       </c>
-      <c r="G33">
+      <c r="G37" s="9">
         <v>0.4617</v>
       </c>
-      <c r="H33">
+      <c r="H37" s="9">
         <v>0.60509999999999997</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" t="s">
+    <row r="38" spans="1:22" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
+        <v>15</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D34">
+      <c r="D38" s="4">
         <v>0.56120000000000003</v>
       </c>
-      <c r="E34">
+      <c r="E38" s="4">
         <v>0.39419999999999999</v>
       </c>
-      <c r="F34">
+      <c r="F38" s="4">
         <v>0.68130000000000002</v>
       </c>
-      <c r="G34">
+      <c r="G38" s="4">
         <v>0.42899999999999999</v>
       </c>
-      <c r="H34">
+      <c r="H38" s="4">
         <v>0.54069999999999996</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>15</v>
-      </c>
-      <c r="C35" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35">
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
+      <c r="P38" s="6"/>
+      <c r="Q38" s="6"/>
+      <c r="R38" s="6"/>
+      <c r="S38" s="6"/>
+      <c r="T38" s="6"/>
+      <c r="U38" s="6"/>
+      <c r="V38" s="6"/>
+    </row>
+    <row r="39" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>15</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39">
         <v>0.57599999999999996</v>
       </c>
-      <c r="E35">
+      <c r="E39">
         <v>0.40710000000000002</v>
       </c>
-      <c r="F35">
+      <c r="F39">
         <v>0.69750000000000001</v>
       </c>
-      <c r="G35">
+      <c r="G39">
         <v>0.44540000000000002</v>
       </c>
-      <c r="H35">
+      <c r="H39">
         <v>0.57499999999999996</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+      <c r="P39" s="6"/>
+      <c r="Q39" s="6"/>
+      <c r="R39" s="6"/>
+      <c r="S39" s="6"/>
+      <c r="T39" s="6"/>
+      <c r="U39" s="6"/>
+      <c r="V39" s="6"/>
+    </row>
+    <row r="40" spans="1:22" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <v>15</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D36">
+      <c r="D40" s="4">
         <v>0.59770000000000001</v>
       </c>
-      <c r="E36">
+      <c r="E40" s="4">
         <v>0.34439999999999998</v>
       </c>
-      <c r="F36">
+      <c r="F40" s="4">
         <v>0.77969999999999995</v>
       </c>
-      <c r="G36">
+      <c r="G40" s="4">
         <v>0.41720000000000002</v>
       </c>
-      <c r="H36">
+      <c r="H40" s="4">
         <v>0.6048</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>15</v>
-      </c>
-      <c r="C37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D37">
-        <v>0.58409999999999995</v>
-      </c>
-      <c r="E37">
-        <v>0.37659999999999999</v>
-      </c>
-      <c r="F37">
-        <v>0.73329999999999995</v>
-      </c>
-      <c r="G37">
-        <v>0.43099999999999999</v>
-      </c>
-      <c r="H37">
-        <v>0.59550000000000003</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38">
-        <v>0.54139999999999999</v>
-      </c>
-      <c r="E38">
-        <v>0.44040000000000001</v>
-      </c>
-      <c r="F38">
-        <v>0.61409999999999998</v>
-      </c>
-      <c r="G38">
-        <v>0.44540000000000002</v>
-      </c>
-      <c r="H38">
-        <v>0.53210000000000002</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39">
-        <v>0.58079999999999998</v>
-      </c>
-      <c r="E39">
-        <v>0.4123</v>
-      </c>
-      <c r="F39">
-        <v>0.70179999999999998</v>
-      </c>
-      <c r="G39">
-        <v>0.45129999999999998</v>
-      </c>
-      <c r="H39">
-        <v>0.58169999999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="s">
-        <v>11</v>
-      </c>
-      <c r="D40">
-        <v>0.59350000000000003</v>
-      </c>
-      <c r="E40">
-        <v>0.503</v>
-      </c>
-      <c r="F40">
-        <v>0.65859999999999996</v>
-      </c>
-      <c r="G40">
-        <v>0.50860000000000005</v>
-      </c>
-      <c r="H40">
-        <v>0.61560000000000004</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
+      <c r="P40" s="6"/>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="6"/>
+      <c r="S40" s="6"/>
+      <c r="T40" s="6"/>
+      <c r="U40" s="6"/>
+      <c r="V40" s="6"/>
+    </row>
+    <row r="41" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>15</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
       </c>
       <c r="D41">
+        <v>0.58409999999999995</v>
+      </c>
+      <c r="E41">
+        <v>0.37659999999999999</v>
+      </c>
+      <c r="F41">
+        <v>0.73329999999999995</v>
+      </c>
+      <c r="G41">
+        <v>0.43099999999999999</v>
+      </c>
+      <c r="H41">
+        <v>0.59550000000000003</v>
+      </c>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="6"/>
+      <c r="Q41" s="6"/>
+      <c r="R41" s="6"/>
+      <c r="S41" s="6"/>
+      <c r="T41" s="6"/>
+      <c r="U41" s="6"/>
+      <c r="V41" s="6"/>
+    </row>
+    <row r="42" spans="1:22" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>15</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="7">
+        <v>0.54139999999999999</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.44040000000000001</v>
+      </c>
+      <c r="F42" s="7">
+        <v>0.61409999999999998</v>
+      </c>
+      <c r="G42" s="7">
+        <v>0.44540000000000002</v>
+      </c>
+      <c r="H42" s="7">
+        <v>0.53210000000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="9">
+        <v>15</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="9">
+        <v>0.58079999999999998</v>
+      </c>
+      <c r="E43" s="9">
+        <v>0.4123</v>
+      </c>
+      <c r="F43" s="9">
+        <v>0.70179999999999998</v>
+      </c>
+      <c r="G43" s="9">
+        <v>0.45129999999999998</v>
+      </c>
+      <c r="H43" s="9">
+        <v>0.58169999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>15</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="7">
+        <v>0.59350000000000003</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.503</v>
+      </c>
+      <c r="F44" s="7">
+        <v>0.65859999999999996</v>
+      </c>
+      <c r="G44" s="7">
+        <v>0.50860000000000005</v>
+      </c>
+      <c r="H44" s="7">
+        <v>0.61560000000000004</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="9">
+        <v>15</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="9">
         <v>0.58930000000000005</v>
       </c>
-      <c r="E41">
+      <c r="E45" s="9">
         <v>0.4178</v>
       </c>
-      <c r="F41">
+      <c r="F45" s="9">
         <v>0.71250000000000002</v>
       </c>
-      <c r="G41">
+      <c r="G45" s="9">
         <v>0.4597</v>
       </c>
-      <c r="H41">
+      <c r="H45" s="9">
         <v>0.60209999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42">
+    <row r="46" spans="1:22" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
         <v>29</v>
       </c>
-      <c r="B42" t="s">
-        <v>17</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B46" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D42">
+      <c r="D46" s="4">
         <v>0.54349999999999998</v>
       </c>
-      <c r="E42">
+      <c r="E46" s="4">
         <v>0.47310000000000002</v>
       </c>
-      <c r="F42">
+      <c r="F46" s="4">
         <v>0.59419999999999995</v>
       </c>
-      <c r="G42">
+      <c r="G46" s="4">
         <v>0.46429999999999999</v>
       </c>
-      <c r="H42">
+      <c r="H46" s="4">
         <v>0.53400000000000003</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43">
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6"/>
+      <c r="P46" s="6"/>
+      <c r="Q46" s="6"/>
+      <c r="R46" s="6"/>
+      <c r="S46" s="6"/>
+      <c r="T46" s="6"/>
+      <c r="U46" s="6"/>
+      <c r="V46" s="6"/>
+    </row>
+    <row r="47" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47">
         <v>29</v>
       </c>
-      <c r="B43" t="s">
-        <v>17</v>
-      </c>
-      <c r="C43" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43">
+      <c r="B47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47">
         <v>0.59660000000000002</v>
       </c>
-      <c r="E43">
+      <c r="E47">
         <v>0.36280000000000001</v>
       </c>
-      <c r="F43">
+      <c r="F47">
         <v>0.76470000000000005</v>
       </c>
-      <c r="G43">
+      <c r="G47">
         <v>0.42930000000000001</v>
       </c>
-      <c r="H43">
+      <c r="H47">
         <v>0.60899999999999999</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44">
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
+      <c r="P47" s="6"/>
+      <c r="Q47" s="6"/>
+      <c r="R47" s="6"/>
+      <c r="S47" s="6"/>
+      <c r="T47" s="6"/>
+      <c r="U47" s="6"/>
+      <c r="V47" s="6"/>
+    </row>
+    <row r="48" spans="1:22" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
         <v>29</v>
       </c>
-      <c r="B44" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="B48" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D44">
+      <c r="D48" s="4">
         <v>0.59650000000000003</v>
       </c>
-      <c r="E44">
+      <c r="E48" s="4">
         <v>0.42959999999999998</v>
       </c>
-      <c r="F44">
+      <c r="F48" s="4">
         <v>0.71650000000000003</v>
       </c>
-      <c r="G44">
+      <c r="G48" s="4">
         <v>0.47110000000000002</v>
       </c>
-      <c r="H44">
+      <c r="H48" s="4">
         <v>0.6099</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45">
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6"/>
+      <c r="P48" s="6"/>
+      <c r="Q48" s="6"/>
+      <c r="R48" s="6"/>
+      <c r="S48" s="6"/>
+      <c r="T48" s="6"/>
+      <c r="U48" s="6"/>
+      <c r="V48" s="6"/>
+    </row>
+    <row r="49" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49">
         <v>29</v>
       </c>
-      <c r="B45" t="s">
-        <v>17</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B49" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" t="s">
         <v>12</v>
       </c>
-      <c r="D45">
+      <c r="D49">
         <v>0.58509999999999995</v>
       </c>
-      <c r="E45">
+      <c r="E49">
         <v>0.41839999999999999</v>
       </c>
-      <c r="F45">
+      <c r="F49">
         <v>0.70499999999999996</v>
       </c>
-      <c r="G45">
+      <c r="G49">
         <v>0.45750000000000002</v>
       </c>
-      <c r="H45">
+      <c r="H49">
         <v>0.59750000000000003</v>
       </c>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="6"/>
+      <c r="P49" s="6"/>
+      <c r="Q49" s="6"/>
+      <c r="R49" s="6"/>
+      <c r="S49" s="6"/>
+      <c r="T49" s="6"/>
+      <c r="U49" s="6"/>
+      <c r="V49" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1635,1045 +2164,1325 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="18.140625" customWidth="1"/>
+    <col min="1" max="7" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
       </c>
       <c r="D2">
-        <v>3631</v>
+        <v>3337</v>
       </c>
       <c r="E2">
-        <v>1430</v>
+        <v>1724</v>
       </c>
       <c r="F2">
-        <v>2194</v>
+        <v>2383</v>
       </c>
       <c r="G2">
-        <v>1444</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>3556</v>
+        <v>3352</v>
       </c>
       <c r="E3">
-        <v>1505</v>
+        <v>1709</v>
       </c>
       <c r="F3">
-        <v>2135</v>
+        <v>2262</v>
       </c>
       <c r="G3">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>2722</v>
+        <v>2020</v>
       </c>
       <c r="E4">
-        <v>2339</v>
+        <v>3041</v>
       </c>
       <c r="F4">
-        <v>1335</v>
+        <v>1099</v>
       </c>
       <c r="G4">
-        <v>2303</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
       <c r="D5">
-        <v>3674</v>
+        <v>3690</v>
       </c>
       <c r="E5">
-        <v>1387</v>
+        <v>1371</v>
       </c>
       <c r="F5">
-        <v>2150</v>
+        <v>2497</v>
       </c>
       <c r="G5">
-        <v>1488</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
       <c r="D6">
-        <v>3792</v>
+        <v>3631</v>
       </c>
       <c r="E6">
-        <v>1269</v>
+        <v>1430</v>
       </c>
       <c r="F6">
-        <v>2320</v>
+        <v>2194</v>
       </c>
       <c r="G6">
-        <v>1318</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
       <c r="D7">
-        <v>3688</v>
+        <v>3556</v>
       </c>
       <c r="E7">
-        <v>1373</v>
+        <v>1505</v>
       </c>
       <c r="F7">
-        <v>2250</v>
+        <v>2135</v>
       </c>
       <c r="G7">
-        <v>1388</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>10</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
       </c>
       <c r="D8">
-        <v>2639</v>
+        <v>2722</v>
       </c>
       <c r="E8">
-        <v>2422</v>
+        <v>2339</v>
       </c>
       <c r="F8">
-        <v>1280</v>
+        <v>1335</v>
       </c>
       <c r="G8">
-        <v>2358</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>10</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
       </c>
       <c r="D9">
-        <v>3802</v>
+        <v>3674</v>
       </c>
       <c r="E9">
-        <v>1259</v>
+        <v>1387</v>
       </c>
       <c r="F9">
-        <v>2288</v>
+        <v>2150</v>
       </c>
       <c r="G9">
-        <v>1350</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>3409</v>
+        <v>3792</v>
       </c>
       <c r="E10">
-        <v>1652</v>
+        <v>1269</v>
       </c>
       <c r="F10">
-        <v>2141</v>
+        <v>2320</v>
       </c>
       <c r="G10">
-        <v>1497</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11">
-        <v>3469</v>
+        <v>3688</v>
       </c>
       <c r="E11">
-        <v>1592</v>
+        <v>1373</v>
       </c>
       <c r="F11">
-        <v>2059</v>
+        <v>2250</v>
       </c>
       <c r="G11">
-        <v>1579</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
       </c>
       <c r="D12">
-        <v>3134</v>
+        <v>2639</v>
       </c>
       <c r="E12">
-        <v>1927</v>
+        <v>2422</v>
       </c>
       <c r="F12">
-        <v>1642</v>
+        <v>1280</v>
       </c>
       <c r="G12">
-        <v>1996</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13">
-        <v>3615</v>
+        <v>3802</v>
       </c>
       <c r="E13">
-        <v>1446</v>
+        <v>1259</v>
       </c>
       <c r="F13">
-        <v>2140</v>
+        <v>2288</v>
       </c>
       <c r="G13">
-        <v>1498</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
         <v>9</v>
       </c>
       <c r="D14">
-        <v>3689</v>
+        <v>3409</v>
       </c>
       <c r="E14">
-        <v>1372</v>
+        <v>1652</v>
       </c>
       <c r="F14">
-        <v>2298</v>
+        <v>2141</v>
       </c>
       <c r="G14">
-        <v>1340</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>10</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
       </c>
       <c r="D15">
-        <v>3562</v>
+        <v>3469</v>
       </c>
       <c r="E15">
-        <v>1499</v>
+        <v>1592</v>
       </c>
       <c r="F15">
-        <v>2154</v>
+        <v>2059</v>
       </c>
       <c r="G15">
-        <v>1484</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>10</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16">
-        <v>4433</v>
+        <v>3134</v>
       </c>
       <c r="E16">
-        <v>628</v>
+        <v>1927</v>
       </c>
       <c r="F16">
-        <v>2930</v>
+        <v>1642</v>
       </c>
       <c r="G16">
-        <v>708</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>10</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
       </c>
       <c r="D17">
-        <v>3805</v>
+        <v>3615</v>
       </c>
       <c r="E17">
-        <v>1256</v>
+        <v>1446</v>
       </c>
       <c r="F17">
-        <v>2305</v>
+        <v>2140</v>
       </c>
       <c r="G17">
-        <v>1333</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>10</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C18" t="s">
         <v>9</v>
       </c>
       <c r="D18">
-        <v>3415</v>
+        <v>3689</v>
       </c>
       <c r="E18">
-        <v>1646</v>
+        <v>1372</v>
       </c>
       <c r="F18">
-        <v>2206</v>
+        <v>2298</v>
       </c>
       <c r="G18">
-        <v>1432</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>10</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
       </c>
       <c r="D19">
-        <v>3397</v>
+        <v>3562</v>
       </c>
       <c r="E19">
-        <v>1664</v>
+        <v>1499</v>
       </c>
       <c r="F19">
-        <v>2113</v>
+        <v>2154</v>
       </c>
       <c r="G19">
-        <v>1525</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>10</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
       </c>
       <c r="D20">
-        <v>3531</v>
+        <v>4433</v>
       </c>
       <c r="E20">
-        <v>1530</v>
+        <v>628</v>
       </c>
       <c r="F20">
-        <v>2008</v>
+        <v>2930</v>
       </c>
       <c r="G20">
-        <v>1630</v>
+        <v>708</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>10</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
       </c>
       <c r="D21">
-        <v>3588</v>
+        <v>3805</v>
       </c>
       <c r="E21">
-        <v>1473</v>
+        <v>1256</v>
       </c>
       <c r="F21">
-        <v>2109</v>
+        <v>2305</v>
       </c>
       <c r="G21">
-        <v>1529</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C22" t="s">
         <v>9</v>
       </c>
       <c r="D22">
-        <v>3163</v>
+        <v>3415</v>
       </c>
       <c r="E22">
-        <v>1898</v>
+        <v>1646</v>
       </c>
       <c r="F22">
-        <v>2020</v>
+        <v>2206</v>
       </c>
       <c r="G22">
-        <v>1618</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
       </c>
       <c r="D23">
-        <v>3516</v>
+        <v>3397</v>
       </c>
       <c r="E23">
-        <v>1545</v>
+        <v>1664</v>
       </c>
       <c r="F23">
-        <v>2089</v>
+        <v>2113</v>
       </c>
       <c r="G23">
-        <v>1549</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
       </c>
       <c r="D24">
-        <v>3001</v>
+        <v>3531</v>
       </c>
       <c r="E24">
-        <v>2060</v>
+        <v>1530</v>
       </c>
       <c r="F24">
-        <v>1509</v>
+        <v>2008</v>
       </c>
       <c r="G24">
-        <v>2129</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
       </c>
       <c r="D25">
-        <v>3582</v>
+        <v>3588</v>
       </c>
       <c r="E25">
-        <v>1479</v>
+        <v>1473</v>
       </c>
       <c r="F25">
-        <v>2078</v>
+        <v>2109</v>
       </c>
       <c r="G25">
-        <v>1560</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>15</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
       </c>
       <c r="D26">
-        <v>3222</v>
+        <v>3163</v>
       </c>
       <c r="E26">
-        <v>1839</v>
+        <v>1898</v>
       </c>
       <c r="F26">
-        <v>2033</v>
+        <v>2020</v>
       </c>
       <c r="G26">
-        <v>1605</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>15</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
       </c>
       <c r="D27">
-        <v>3471</v>
+        <v>3516</v>
       </c>
       <c r="E27">
-        <v>1590</v>
+        <v>1545</v>
       </c>
       <c r="F27">
-        <v>2027</v>
+        <v>2089</v>
       </c>
       <c r="G27">
-        <v>1611</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>15</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
       </c>
       <c r="D28">
-        <v>2617</v>
+        <v>3001</v>
       </c>
       <c r="E28">
-        <v>2444</v>
+        <v>2060</v>
       </c>
       <c r="F28">
-        <v>1235</v>
+        <v>1509</v>
       </c>
       <c r="G28">
-        <v>2403</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>15</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
       </c>
       <c r="D29">
-        <v>3583</v>
+        <v>3582</v>
       </c>
       <c r="E29">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="F29">
-        <v>2058</v>
+        <v>2078</v>
       </c>
       <c r="G29">
-        <v>1580</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>15</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
       </c>
       <c r="D30">
-        <v>3189</v>
+        <v>3222</v>
       </c>
       <c r="E30">
-        <v>1872</v>
+        <v>1839</v>
       </c>
       <c r="F30">
-        <v>1964</v>
+        <v>2033</v>
       </c>
       <c r="G30">
-        <v>1674</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>15</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C31" t="s">
         <v>10</v>
       </c>
       <c r="D31">
-        <v>3660</v>
+        <v>3471</v>
       </c>
       <c r="E31">
-        <v>1401</v>
+        <v>1590</v>
       </c>
       <c r="F31">
-        <v>2147</v>
+        <v>2027</v>
       </c>
       <c r="G31">
-        <v>1491</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>15</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
       </c>
       <c r="D32">
-        <v>3168</v>
+        <v>2617</v>
       </c>
       <c r="E32">
-        <v>1893</v>
+        <v>2444</v>
       </c>
       <c r="F32">
-        <v>1671</v>
+        <v>1235</v>
       </c>
       <c r="G32">
-        <v>1967</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>15</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
       </c>
       <c r="D33">
-        <v>3608</v>
+        <v>3583</v>
       </c>
       <c r="E33">
-        <v>1453</v>
+        <v>1478</v>
       </c>
       <c r="F33">
-        <v>2110</v>
+        <v>2058</v>
       </c>
       <c r="G33">
-        <v>1528</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>15</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C34" t="s">
         <v>9</v>
       </c>
       <c r="D34">
-        <v>3448</v>
+        <v>3189</v>
       </c>
       <c r="E34">
-        <v>1613</v>
+        <v>1872</v>
       </c>
       <c r="F34">
-        <v>2204</v>
+        <v>1964</v>
       </c>
       <c r="G34">
-        <v>1434</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>15</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C35" t="s">
         <v>10</v>
       </c>
       <c r="D35">
-        <v>3530</v>
+        <v>3660</v>
       </c>
       <c r="E35">
-        <v>1531</v>
+        <v>1401</v>
       </c>
       <c r="F35">
-        <v>2157</v>
+        <v>2147</v>
       </c>
       <c r="G35">
-        <v>1481</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>15</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C36" t="s">
         <v>11</v>
       </c>
       <c r="D36">
-        <v>3946</v>
+        <v>3168</v>
       </c>
       <c r="E36">
-        <v>1115</v>
+        <v>1893</v>
       </c>
       <c r="F36">
-        <v>2385</v>
+        <v>1671</v>
       </c>
       <c r="G36">
-        <v>1253</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>15</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
       </c>
       <c r="D37">
-        <v>3711</v>
+        <v>3608</v>
       </c>
       <c r="E37">
-        <v>1350</v>
+        <v>1453</v>
       </c>
       <c r="F37">
-        <v>2268</v>
+        <v>2110</v>
       </c>
       <c r="G37">
-        <v>1370</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>15</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C38" t="s">
         <v>9</v>
       </c>
       <c r="D38">
-        <v>3108</v>
+        <v>3448</v>
       </c>
       <c r="E38">
-        <v>1953</v>
+        <v>1613</v>
       </c>
       <c r="F38">
-        <v>2036</v>
+        <v>2204</v>
       </c>
       <c r="G38">
-        <v>1602</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>15</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C39" t="s">
         <v>10</v>
       </c>
       <c r="D39">
-        <v>3552</v>
+        <v>3530</v>
       </c>
       <c r="E39">
-        <v>1509</v>
+        <v>1531</v>
       </c>
       <c r="F39">
-        <v>2138</v>
+        <v>2157</v>
       </c>
       <c r="G39">
-        <v>1500</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>15</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C40" t="s">
         <v>11</v>
       </c>
       <c r="D40">
-        <v>3333</v>
+        <v>3946</v>
       </c>
       <c r="E40">
-        <v>1728</v>
+        <v>1115</v>
       </c>
       <c r="F40">
-        <v>1808</v>
+        <v>2385</v>
       </c>
       <c r="G40">
-        <v>1830</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>15</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
       </c>
       <c r="D41">
-        <v>3606</v>
+        <v>3711</v>
       </c>
       <c r="E41">
-        <v>1455</v>
+        <v>1350</v>
       </c>
       <c r="F41">
-        <v>2118</v>
+        <v>2268</v>
       </c>
       <c r="G41">
-        <v>1520</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>29</v>
-      </c>
-      <c r="B42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C42" t="s">
         <v>9</v>
       </c>
       <c r="D42">
-        <v>3007</v>
+        <v>3108</v>
       </c>
       <c r="E42">
-        <v>2054</v>
+        <v>1953</v>
       </c>
       <c r="F42">
-        <v>1917</v>
+        <v>2036</v>
       </c>
       <c r="G42">
-        <v>1721</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>29</v>
-      </c>
-      <c r="B43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C43" t="s">
         <v>10</v>
       </c>
       <c r="D43">
-        <v>3870</v>
+        <v>3552</v>
       </c>
       <c r="E43">
-        <v>1191</v>
+        <v>1509</v>
       </c>
       <c r="F43">
-        <v>2318</v>
+        <v>2138</v>
       </c>
       <c r="G43">
-        <v>1320</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>29</v>
-      </c>
-      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C44" t="s">
         <v>11</v>
       </c>
       <c r="D44">
-        <v>3626</v>
+        <v>3333</v>
       </c>
       <c r="E44">
-        <v>1435</v>
+        <v>1728</v>
       </c>
       <c r="F44">
-        <v>2075</v>
+        <v>1808</v>
       </c>
       <c r="G44">
-        <v>1563</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>29</v>
-      </c>
-      <c r="B45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C45" t="s">
         <v>12</v>
       </c>
       <c r="D45">
+        <v>3606</v>
+      </c>
+      <c r="E45">
+        <v>1455</v>
+      </c>
+      <c r="F45">
+        <v>2118</v>
+      </c>
+      <c r="G45">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>29</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46">
+        <v>3007</v>
+      </c>
+      <c r="E46">
+        <v>2054</v>
+      </c>
+      <c r="F46">
+        <v>1917</v>
+      </c>
+      <c r="G46">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>29</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47">
+        <v>3870</v>
+      </c>
+      <c r="E47">
+        <v>1191</v>
+      </c>
+      <c r="F47">
+        <v>2318</v>
+      </c>
+      <c r="G47">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>29</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48">
+        <v>3626</v>
+      </c>
+      <c r="E48">
+        <v>1435</v>
+      </c>
+      <c r="F48">
+        <v>2075</v>
+      </c>
+      <c r="G48">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>29</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49">
         <v>3568</v>
       </c>
-      <c r="E45">
+      <c r="E49">
         <v>1493</v>
       </c>
-      <c r="F45">
+      <c r="F49">
         <v>2116</v>
       </c>
-      <c r="G45">
+      <c r="G49">
         <v>1522</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="11" width="17.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="C2">
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="D2">
+        <v>0.41089999999999999</v>
+      </c>
+      <c r="E2">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="F2">
+        <v>0.66539999999999999</v>
+      </c>
+      <c r="G2">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="H2">
+        <v>0.43719999999999998</v>
+      </c>
+      <c r="I2">
+        <v>2.3599999999999999E-2</v>
+      </c>
+      <c r="J2">
+        <v>0.55189999999999995</v>
+      </c>
+      <c r="K2">
+        <v>2.1600000000000001E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="12">
+        <v>0.58289999999999997</v>
+      </c>
+      <c r="C3" s="12">
+        <v>2.01E-2</v>
+      </c>
+      <c r="D3" s="12">
+        <v>0.51949999999999996</v>
+      </c>
+      <c r="E3" s="12">
+        <v>0.14660000000000001</v>
+      </c>
+      <c r="F3" s="12">
+        <v>0.62849999999999995</v>
+      </c>
+      <c r="G3" s="12">
+        <v>0.12920000000000001</v>
+      </c>
+      <c r="H3" s="12">
+        <v>0.49930000000000002</v>
+      </c>
+      <c r="I3" s="12">
+        <v>8.0699999999999994E-2</v>
+      </c>
+      <c r="J3" s="12">
+        <v>0.60870000000000002</v>
+      </c>
+      <c r="K3" s="12">
+        <v>1.34E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>0.57889999999999997</v>
+      </c>
+      <c r="C4">
+        <v>1.35E-2</v>
+      </c>
+      <c r="D4">
+        <v>0.40789999999999998</v>
+      </c>
+      <c r="E4">
+        <v>2.3400000000000001E-2</v>
+      </c>
+      <c r="F4">
+        <v>0.70179999999999998</v>
+      </c>
+      <c r="G4">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="H4">
+        <v>0.44740000000000002</v>
+      </c>
+      <c r="I4">
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="J4">
+        <v>0.58379999999999999</v>
+      </c>
+      <c r="K4">
+        <v>1.8599999999999998E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>0.58679999999999999</v>
+      </c>
+      <c r="C5">
+        <v>1.03E-2</v>
+      </c>
+      <c r="D5">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="E5">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="F5">
+        <v>0.72170000000000001</v>
+      </c>
+      <c r="G5">
+        <v>1.66E-2</v>
+      </c>
+      <c r="H5">
+        <v>0.4461</v>
+      </c>
+      <c r="I5">
+        <v>2.7699999999999999E-2</v>
+      </c>
+      <c r="J5">
+        <v>0.59930000000000005</v>
+      </c>
+      <c r="K5">
+        <v>1.9400000000000001E-2</v>
       </c>
     </row>
   </sheetData>
